--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="25726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Product Automation\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5EEC1F61-9896-41A5-91BB-14685F58B924}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20230720-8792-4215-8D7D-2810EB6A5074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="4" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="55">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -120,9 +120,6 @@
     <t>fieldQuestion3__c</t>
   </si>
   <si>
-    <t>fieldsbirEmpNumber__c</t>
-  </si>
-  <si>
     <t>fieldExperienceLevel__c</t>
   </si>
   <si>
@@ -183,22 +180,28 @@
     <t>Automation Testing</t>
   </si>
   <si>
-    <t>fieldAgreement5__c</t>
-  </si>
-  <si>
-    <t>fieldJustification__c</t>
-  </si>
-  <si>
-    <t>fieldProjectBeneficiaries__c</t>
-  </si>
-  <si>
-    <t>fieldProjectGoal__c</t>
-  </si>
-  <si>
-    <t>fieldProjectAbstract__c</t>
-  </si>
-  <si>
     <t>Budget Tab: Budget Summary by Focus Area</t>
+  </si>
+  <si>
+    <t>Agreement5__c</t>
+  </si>
+  <si>
+    <t>Question1__c</t>
+  </si>
+  <si>
+    <t>Question3__c</t>
+  </si>
+  <si>
+    <t>sbirEmpNumber__c</t>
+  </si>
+  <si>
+    <t>ExperienceLevel__c</t>
+  </si>
+  <si>
+    <t>AppplicationSubmitted__c</t>
+  </si>
+  <si>
+    <t>SubmittedOnForm__c</t>
   </si>
 </sst>
 </file>
@@ -296,9 +299,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -336,7 +339,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -442,7 +445,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -584,7 +587,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -593,10 +596,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE61A50-F37E-45CB-A9C9-9EE192BF6C64}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -615,7 +618,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -626,10 +629,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -637,10 +640,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -648,10 +651,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s">
         <v>34</v>
-      </c>
-      <c r="C5" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -662,10 +665,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -684,10 +687,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -695,7 +698,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C3">
         <v>43707</v>
@@ -709,10 +712,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -731,7 +734,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -742,10 +745,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -753,10 +756,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -764,10 +767,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -775,10 +778,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -786,10 +789,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -797,10 +800,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -808,10 +811,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C9" t="s">
         <v>34</v>
-      </c>
-      <c r="C9" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -822,10 +825,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -844,10 +847,10 @@
         <v>10</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>43</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -885,13 +888,13 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B6" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="C6" s="1" t="s">
         <v>46</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -902,10 +905,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -946,10 +949,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -957,7 +960,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C5" t="s">
         <v>25</v>
@@ -968,7 +971,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -982,10 +985,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1019,10 +1022,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.90625" customWidth="1"/>
+    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1041,7 +1044,7 @@
         <v>10</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>52</v>
+        <v>15</v>
       </c>
       <c r="C2" t="s">
         <v>22</v>
@@ -1052,7 +1055,7 @@
         <v>10</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>51</v>
+        <v>16</v>
       </c>
       <c r="C3" t="s">
         <v>21</v>
@@ -1063,7 +1066,7 @@
         <v>10</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -1085,7 +1088,7 @@
         <v>18</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>49</v>
+        <v>14</v>
       </c>
       <c r="C6" t="s">
         <v>19</v>
@@ -1100,10 +1103,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1169,10 +1172,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.90625" customWidth="1"/>
+    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1238,10 +1241,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" customWidth="1"/>
+    <col min="3" max="3" width="20.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1260,7 +1263,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>24</v>
+        <v>49</v>
       </c>
       <c r="C2" t="s">
         <v>25</v>
@@ -1271,7 +1274,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>26</v>
+        <v>50</v>
       </c>
       <c r="C3" t="s">
         <v>25</v>
@@ -1282,7 +1285,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>27</v>
+        <v>51</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -1293,10 +1296,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>28</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1304,7 +1307,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>30</v>
+        <v>53</v>
       </c>
       <c r="C6" t="s">
         <v>25</v>
@@ -1315,7 +1318,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>31</v>
+        <v>54</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1329,10 +1332,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.6640625" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" customWidth="1"/>
+    <col min="2" max="2" width="43.6328125" customWidth="1"/>
+    <col min="3" max="3" width="22.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1351,7 +1354,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -1362,10 +1365,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1373,10 +1376,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1388,10 +1391,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1410,7 +1413,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -1421,10 +1424,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1432,10 +1435,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1443,10 +1446,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1454,10 +1457,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C6" t="s">
         <v>34</v>
-      </c>
-      <c r="C6" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -1469,10 +1472,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1491,10 +1494,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1502,10 +1505,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
         <v>34</v>
-      </c>
-      <c r="C3" t="s">
-        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20230720-8792-4215-8D7D-2810EB6A5074}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFB3A29-51DD-414F-8E8E-DDCA4A3D3971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="4" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
@@ -20,12 +20,13 @@
     <sheet name="Edition1" sheetId="5" r:id="rId5"/>
     <sheet name="Form_Edit" sheetId="6" r:id="rId6"/>
     <sheet name="Negotiation_Edit" sheetId="7" r:id="rId7"/>
-    <sheet name="Nego_Edit1" sheetId="8" r:id="rId8"/>
-    <sheet name="FileFormForms" sheetId="9" r:id="rId9"/>
-    <sheet name="FileFormForms1" sheetId="10" r:id="rId10"/>
-    <sheet name="FileFormForms2" sheetId="11" r:id="rId11"/>
-    <sheet name="Edition_v" sheetId="12" r:id="rId12"/>
-    <sheet name="Form_v" sheetId="13" r:id="rId13"/>
+    <sheet name="Nego_Edit_Notes" sheetId="16" r:id="rId8"/>
+    <sheet name="Nego_Edit1" sheetId="8" r:id="rId9"/>
+    <sheet name="FileFormForms" sheetId="9" r:id="rId10"/>
+    <sheet name="FileFormForms1" sheetId="10" r:id="rId11"/>
+    <sheet name="FileFormForms2" sheetId="11" r:id="rId12"/>
+    <sheet name="Edition_v" sheetId="12" r:id="rId13"/>
+    <sheet name="Form_v" sheetId="13" r:id="rId14"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -37,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="58">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -202,6 +203,15 @@
   </si>
   <si>
     <t>SubmittedOnForm__c</t>
+  </si>
+  <si>
+    <t>RevisionDueDate__c</t>
+  </si>
+  <si>
+    <t>PreApplicationSectionsforRevision__c</t>
+  </si>
+  <si>
+    <t>ExplanationOfRevisionsNeeded__c</t>
   </si>
 </sst>
 </file>
@@ -663,6 +673,53 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -709,7 +766,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -822,7 +879,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -902,7 +959,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -1389,6 +1446,59 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0ADD10-8CE2-43FE-B59D-D33E800DC8BE}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="38.7265625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -1467,51 +1577,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -8,25 +8,24 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFB3A29-51DD-414F-8E8E-DDCA4A3D3971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C1F8AC-FB84-4868-9B63-EB06DD86FE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="7" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
     <sheet name="Creation" sheetId="1" r:id="rId2"/>
     <sheet name="Edition" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId4"/>
-    <sheet name="Edition1" sheetId="5" r:id="rId5"/>
-    <sheet name="Form_Edit" sheetId="6" r:id="rId6"/>
-    <sheet name="Negotiation_Edit" sheetId="7" r:id="rId7"/>
-    <sheet name="Nego_Edit_Notes" sheetId="16" r:id="rId8"/>
-    <sheet name="Nego_Edit1" sheetId="8" r:id="rId9"/>
-    <sheet name="FileFormForms" sheetId="9" r:id="rId10"/>
-    <sheet name="FileFormForms1" sheetId="10" r:id="rId11"/>
-    <sheet name="FileFormForms2" sheetId="11" r:id="rId12"/>
-    <sheet name="Edition_v" sheetId="12" r:id="rId13"/>
-    <sheet name="Form_v" sheetId="13" r:id="rId14"/>
+    <sheet name="Edition1" sheetId="5" r:id="rId4"/>
+    <sheet name="Form_Edit" sheetId="6" r:id="rId5"/>
+    <sheet name="Negotiation_Edit" sheetId="7" r:id="rId6"/>
+    <sheet name="Nego_Edit_Notes" sheetId="16" r:id="rId7"/>
+    <sheet name="Nego_Edit1" sheetId="8" r:id="rId8"/>
+    <sheet name="FileFormForms" sheetId="9" r:id="rId9"/>
+    <sheet name="FileFormForms1" sheetId="10" r:id="rId10"/>
+    <sheet name="FileFormForms2" sheetId="11" r:id="rId11"/>
+    <sheet name="Edition_v" sheetId="12" r:id="rId12"/>
+    <sheet name="Form_v" sheetId="13" r:id="rId13"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -38,14 +37,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="42">
   <si>
     <t>Sub Tab</t>
   </si>
   <si>
-    <t>Field Type</t>
-  </si>
-  <si>
     <t>Field API Name</t>
   </si>
   <si>
@@ -55,30 +51,12 @@
     <t>None</t>
   </si>
   <si>
-    <t>Text</t>
-  </si>
-  <si>
     <t>Title__c</t>
   </si>
   <si>
-    <t>Lookup</t>
-  </si>
-  <si>
-    <t>ProjectDirectorContact__c</t>
-  </si>
-  <si>
-    <t>Automation SPI</t>
-  </si>
-  <si>
     <t>Overview</t>
   </si>
   <si>
-    <t>RichText</t>
-  </si>
-  <si>
-    <t>CheckBox</t>
-  </si>
-  <si>
     <t>Automation Pre-Application Regression</t>
   </si>
   <si>
@@ -112,36 +90,12 @@
     <t>Checked</t>
   </si>
   <si>
-    <t>fieldQuestion1__c</t>
-  </si>
-  <si>
     <t>Automation Test</t>
   </si>
   <si>
-    <t>fieldQuestion3__c</t>
-  </si>
-  <si>
-    <t>fieldExperienceLevel__c</t>
-  </si>
-  <si>
     <t>0-5 years</t>
   </si>
   <si>
-    <t>fieldAppplicationSubmitted__c</t>
-  </si>
-  <si>
-    <t>fieldSubmittedOnForm__c</t>
-  </si>
-  <si>
-    <t>fieldRevisionDueDate__c</t>
-  </si>
-  <si>
-    <t>fieldPreApplicationSectionsforRevision__c</t>
-  </si>
-  <si>
-    <t>fieldExplanationOfRevisionsNeeded__c</t>
-  </si>
-  <si>
     <t>Negotiation Initiated</t>
   </si>
   <si>
@@ -166,18 +120,12 @@
     <t>Budget Tab: Narrative</t>
   </si>
   <si>
-    <t>fieldTitle__c</t>
-  </si>
-  <si>
     <t>Automation Announcement</t>
   </si>
   <si>
     <t>Negotiations</t>
   </si>
   <si>
-    <t>fieldApplicantResponse__c</t>
-  </si>
-  <si>
     <t>Automation Testing</t>
   </si>
   <si>
@@ -212,6 +160,9 @@
   </si>
   <si>
     <t>ExplanationOfRevisionsNeeded__c</t>
+  </si>
+  <si>
+    <t>ApplicantResponse__c</t>
   </si>
 </sst>
 </file>
@@ -617,18 +568,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -636,35 +587,35 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -673,53 +624,6 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -733,29 +637,29 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C3">
         <v>43707</v>
@@ -766,7 +670,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -780,18 +684,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -799,79 +703,79 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>39</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>40</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8" spans="1:3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="9" spans="1:3">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -879,7 +783,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -893,65 +797,65 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>42</v>
+        <v>5</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C5" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>45</v>
+        <v>28</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>41</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -959,7 +863,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -973,62 +877,62 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>26</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>30</v>
+        <v>37</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1053,21 +957,21 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -1090,65 +994,65 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="3" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="3" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" t="s">
         <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="6" t="s">
-        <v>17</v>
-      </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>48</v>
+        <v>31</v>
       </c>
       <c r="C5" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1158,75 +1062,6 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
-  <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="B4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="B5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="B6" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="B7" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" t="s">
-        <v>10</v>
-      </c>
-      <c r="B18" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" t="s">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -1240,54 +1075,54 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>15</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" s="1" t="s">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>17</v>
-      </c>
       <c r="C4" s="1" t="s">
-        <v>20</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -1295,7 +1130,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -1309,40 +1144,40 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>51</v>
+        <v>34</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -1350,32 +1185,32 @@
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>53</v>
+        <v>36</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>54</v>
+        <v>37</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1386,7 +1221,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -1400,18 +1235,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -1419,24 +1254,24 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
@@ -1445,7 +1280,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0ADD10-8CE2-43FE-B59D-D33E800DC8BE}">
   <dimension ref="A1:B5"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -1458,39 +1293,39 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>55</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>56</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>57</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -1498,7 +1333,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
@@ -1512,18 +1347,18 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>38</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -1531,50 +1366,97 @@
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>36</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>37</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>38</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>3</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="C3" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38C1F8AC-FB84-4868-9B63-EB06DD86FE94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{392C22E0-148C-47F6-9B77-38F47DAC5844}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="7" activeTab="12" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="5" activeTab="6" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="192" uniqueCount="43">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -163,6 +163,9 @@
   </si>
   <si>
     <t>ApplicantResponse__c</t>
+  </si>
+  <si>
+    <t>Files and Forms: Notes</t>
   </si>
 </sst>
 </file>
@@ -1282,50 +1285,66 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0ADD10-8CE2-43FE-B59D-D33E800DC8BE}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="38.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2">
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="4" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>3</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="4" spans="1:2">
+      <c r="C3" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4" s="4" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
+      <c r="C4" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="4" t="s">
         <v>40</v>
+      </c>
+      <c r="C5" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BFB3A29-51DD-414F-8E8E-DDCA4A3D3971}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91D89F1-48A5-4490-A803-CB1BF07EE6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="7" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
@@ -28,10 +28,21 @@
     <sheet name="Edition_v" sheetId="12" r:id="rId13"/>
     <sheet name="Form_v" sheetId="13" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="179017"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -606,10 +617,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE61A50-F37E-45CB-A9C9-9EE192BF6C64}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -628,7 +639,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>55</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -639,7 +650,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>47</v>
@@ -650,7 +661,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>56</v>
       </c>
       <c r="C4" s="7" t="s">
         <v>40</v>
@@ -661,7 +672,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>33</v>
+        <v>57</v>
       </c>
       <c r="C5" t="s">
         <v>34</v>
@@ -675,10 +686,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -722,10 +733,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -769,10 +780,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -882,10 +893,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -962,10 +973,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1042,10 +1053,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1079,10 +1090,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.90625" customWidth="1"/>
-    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1160,10 +1171,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1229,10 +1240,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.90625" customWidth="1"/>
-    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1298,10 +1309,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.54296875" customWidth="1"/>
-    <col min="3" max="3" width="20.36328125" customWidth="1"/>
+    <col min="2" max="2" width="29.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1389,10 +1400,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.6328125" customWidth="1"/>
-    <col min="3" max="3" width="22.54296875" customWidth="1"/>
+    <col min="2" max="2" width="43.6640625" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1448,9 +1459,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0ADD10-8CE2-43FE-B59D-D33E800DC8BE}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="38.7265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1501,10 +1512,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\LwcNew1\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F91D89F1-48A5-4490-A803-CB1BF07EE6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5CA0F7-F9D8-4281-9FA3-82B3F81331BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="49">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -123,36 +123,12 @@
     <t>Checked</t>
   </si>
   <si>
-    <t>fieldQuestion1__c</t>
-  </si>
-  <si>
     <t>Automation Test</t>
   </si>
   <si>
-    <t>fieldQuestion3__c</t>
-  </si>
-  <si>
-    <t>fieldExperienceLevel__c</t>
-  </si>
-  <si>
     <t>0-5 years</t>
   </si>
   <si>
-    <t>fieldAppplicationSubmitted__c</t>
-  </si>
-  <si>
-    <t>fieldSubmittedOnForm__c</t>
-  </si>
-  <si>
-    <t>fieldRevisionDueDate__c</t>
-  </si>
-  <si>
-    <t>fieldPreApplicationSectionsforRevision__c</t>
-  </si>
-  <si>
-    <t>fieldExplanationOfRevisionsNeeded__c</t>
-  </si>
-  <si>
     <t>Negotiation Initiated</t>
   </si>
   <si>
@@ -177,18 +153,12 @@
     <t>Budget Tab: Narrative</t>
   </si>
   <si>
-    <t>fieldTitle__c</t>
-  </si>
-  <si>
     <t>Automation Announcement</t>
   </si>
   <si>
     <t>Negotiations</t>
   </si>
   <si>
-    <t>fieldApplicantResponse__c</t>
-  </si>
-  <si>
     <t>Automation Testing</t>
   </si>
   <si>
@@ -223,6 +193,9 @@
   </si>
   <si>
     <t>ExplanationOfRevisionsNeeded__c</t>
+  </si>
+  <si>
+    <t>ApplicantResponse__c</t>
   </si>
 </sst>
 </file>
@@ -617,10 +590,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE61A50-F37E-45CB-A9C9-9EE192BF6C64}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -639,7 +612,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -650,10 +623,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>47</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -661,10 +634,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -672,10 +645,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
       <c r="C5" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -686,10 +659,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -708,10 +681,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -719,10 +692,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C3" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -733,10 +706,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -755,10 +728,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -766,7 +739,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C3">
         <v>43707</v>
@@ -780,10 +753,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -802,7 +775,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -813,10 +786,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -824,10 +797,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -835,10 +808,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -846,10 +819,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="5" t="s">
         <v>32</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -857,10 +830,10 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -868,10 +841,10 @@
         <v>4</v>
       </c>
       <c r="B8" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -879,10 +852,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="4" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -893,10 +866,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -914,11 +887,11 @@
       <c r="A2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="6" t="s">
-        <v>42</v>
+      <c r="B2" s="1" t="s">
+        <v>6</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -956,13 +929,13 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="B6" s="6" t="s">
-        <v>45</v>
+        <v>35</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>48</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>46</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -973,10 +946,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -995,10 +968,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" t="s">
         <v>24</v>
-      </c>
-      <c r="C2" t="s">
-        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1006,10 +979,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>26</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1017,10 +990,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>27</v>
+        <v>42</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1028,10 +1001,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>43</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1039,7 +1012,7 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="C6">
         <v>5</v>
@@ -1053,10 +1026,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1090,10 +1063,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.90625" customWidth="1"/>
+    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1145,7 +1118,7 @@
         <v>10</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>48</v>
+        <v>38</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
@@ -1171,10 +1144,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.90625" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1240,10 +1213,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.90625" customWidth="1"/>
+    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1309,10 +1282,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" customWidth="1"/>
+    <col min="3" max="3" width="20.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1331,10 +1304,10 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1342,10 +1315,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1353,7 +1326,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="C4">
         <v>9</v>
@@ -1364,10 +1337,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>52</v>
+        <v>42</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1375,10 +1348,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>53</v>
+        <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1386,7 +1359,7 @@
         <v>4</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -1400,10 +1373,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.6640625" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" customWidth="1"/>
+    <col min="2" max="2" width="43.6328125" customWidth="1"/>
+    <col min="3" max="3" width="22.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1422,7 +1395,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -1433,10 +1406,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C3" t="s">
-        <v>35</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1444,10 +1417,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -1459,9 +1432,9 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0ADD10-8CE2-43FE-B59D-D33E800DC8BE}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1477,7 +1450,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>55</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -1485,7 +1458,7 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1493,7 +1466,7 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>56</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1501,7 +1474,7 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>57</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1512,10 +1485,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1534,7 +1507,7 @@
         <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>31</v>
+        <v>45</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -1545,10 +1518,10 @@
         <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C3" s="5" t="s">
-        <v>36</v>
+        <v>28</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1556,10 +1529,10 @@
         <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C4" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1567,10 +1540,10 @@
         <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>32</v>
+        <v>46</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
     </row>
     <row r="6" spans="1:3">
@@ -1578,10 +1551,10 @@
         <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>33</v>
+        <v>47</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,30 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\Workplace\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductClassic\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8AF3C0B-335B-4A82-8F69-352812868F34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F932A1-CB9F-40EF-910E-5C8DCE140DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="6" activeTab="11" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
-    <sheet name="Creation" sheetId="1" r:id="rId1"/>
-    <sheet name="Edition" sheetId="4" r:id="rId2"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId3"/>
-    <sheet name="Edition1" sheetId="5" r:id="rId4"/>
-    <sheet name="Form_Edit" sheetId="6" r:id="rId5"/>
-    <sheet name="Negotiation_Edit" sheetId="7" r:id="rId6"/>
-    <sheet name="Nego_Edit1" sheetId="8" r:id="rId7"/>
-    <sheet name="FileFormForms" sheetId="9" r:id="rId8"/>
-    <sheet name="FileFormForms1" sheetId="10" r:id="rId9"/>
-    <sheet name="FileFormForms2" sheetId="11" r:id="rId10"/>
-    <sheet name="Edition_v" sheetId="12" r:id="rId11"/>
-    <sheet name="Form_v" sheetId="13" r:id="rId12"/>
+    <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
+    <sheet name="Creation" sheetId="1" r:id="rId2"/>
+    <sheet name="Edition" sheetId="4" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId4"/>
+    <sheet name="Edition1" sheetId="5" r:id="rId5"/>
+    <sheet name="Form_EditNewValidate" sheetId="17" r:id="rId6"/>
+    <sheet name="Form_Edit" sheetId="6" r:id="rId7"/>
+    <sheet name="Negotiation_Edit" sheetId="7" r:id="rId8"/>
+    <sheet name="Nego_Edit_Notes" sheetId="16" r:id="rId9"/>
+    <sheet name="Nego_Edit1" sheetId="8" r:id="rId10"/>
+    <sheet name="FileFormForms" sheetId="9" r:id="rId11"/>
+    <sheet name="FileFormForms1" sheetId="10" r:id="rId12"/>
+    <sheet name="FileFormForms2" sheetId="11" r:id="rId13"/>
+    <sheet name="Edition_v" sheetId="12" r:id="rId14"/>
+    <sheet name="Form_v" sheetId="13" r:id="rId15"/>
   </sheets>
   <calcPr calcId="179017"/>
   <extLst>
@@ -36,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="177" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="55">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -110,9 +113,6 @@
     <t>Checked</t>
   </si>
   <si>
-    <t>Agreement5__c</t>
-  </si>
-  <si>
     <t>fieldQuestion1__c</t>
   </si>
   <si>
@@ -183,6 +183,27 @@
   </si>
   <si>
     <t>Automation Testing</t>
+  </si>
+  <si>
+    <t>fieldAgreement5__c</t>
+  </si>
+  <si>
+    <t>fieldJustification__c</t>
+  </si>
+  <si>
+    <t>fieldProjectBeneficiaries__c</t>
+  </si>
+  <si>
+    <t>fieldProjectGoal__c</t>
+  </si>
+  <si>
+    <t>fieldProjectAbstract__c</t>
+  </si>
+  <si>
+    <t>Budget Tab: Budget Summary by Focus Area</t>
+  </si>
+  <si>
+    <t>Files and Forms: Notes</t>
   </si>
 </sst>
 </file>
@@ -196,12 +217,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="7"/>
-      <color rgb="FF222222"/>
-      <name val="Consolas"/>
-      <family val="3"/>
     </font>
     <font>
       <sz val="9"/>
@@ -220,6 +235,12 @@
       <sz val="7"/>
       <color rgb="FF202124"/>
       <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="9.8000000000000007"/>
+      <color rgb="FF297BDE"/>
+      <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
   </fonts>
@@ -255,11 +276,13 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -278,9 +301,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -318,7 +341,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -424,7 +447,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -566,19 +589,19 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
-  <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE61A50-F37E-45CB-A9C9-9EE192BF6C64}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -588,7 +611,7 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
@@ -596,26 +619,58 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>13</v>
+      <c r="B2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C5" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
-  <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -633,8 +688,8 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>33</v>
+      <c r="B2" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -644,91 +699,59 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>38</v>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>39</v>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>41</v>
+      <c r="B5" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C6" s="6" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8" t="s">
-        <v>4</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9" t="s">
-        <v>4</v>
-      </c>
-      <c r="B9" s="5" t="s">
+      <c r="C6" t="s">
         <v>35</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -743,58 +766,25 @@
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B2" s="7" t="s">
-        <v>44</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>45</v>
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3">
-      <c r="A3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B5" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="1" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" s="1" t="s">
-        <v>48</v>
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C3" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>
@@ -803,12 +793,12 @@
 </file>
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -826,55 +816,22 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>25</v>
+      <c r="B2" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C2" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="C6">
-        <v>5</v>
+      <c r="C3">
+        <v>43707</v>
       </c>
     </row>
   </sheetData>
@@ -882,13 +839,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
+  <dimension ref="A1:C9"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -898,63 +855,292 @@
       <c r="B1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:3">
       <c r="A2" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="C2" t="s">
-        <v>22</v>
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C3" t="s">
-        <v>21</v>
+        <v>33</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="C4" t="s">
-        <v>20</v>
+        <v>33</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:3">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C5" t="s">
-        <v>23</v>
+        <v>33</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>19</v>
+        <v>33</v>
+      </c>
+      <c r="C6" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>43</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>47</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
+  <dimension ref="A1:C2"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -964,12 +1150,93 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>52</v>
+      </c>
+      <c r="C2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="C4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="C5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6" s="6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" customWidth="1"/>
-    <col min="2" max="2" width="11.5546875" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="11.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1032,13 +1299,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="21.88671875" customWidth="1"/>
-    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.85546875" customWidth="1"/>
+    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1101,13 +1368,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
-  <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD30DDC9-54F2-4EA2-B2D6-C4D0607FC1E9}">
+  <dimension ref="A1:C3"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="29.5546875" customWidth="1"/>
-    <col min="3" max="3" width="20.33203125" customWidth="1"/>
+    <col min="2" max="2" width="30.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1125,66 +1391,22 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
         <v>25</v>
-      </c>
-      <c r="C2" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>27</v>
+      <c r="B3" s="4" t="s">
+        <v>30</v>
       </c>
       <c r="C3" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1192,13 +1414,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.6640625" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" customWidth="1"/>
+    <col min="2" max="2" width="29.5703125" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1216,48 +1438,80 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C2">
-        <v>43707</v>
+      <c r="B2" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C2" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>34</v>
+      <c r="B3" s="4" t="s">
+        <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>37</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
+      <c r="B4" s="4" t="s">
+        <v>27</v>
+      </c>
+      <c r="C4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>30</v>
+      </c>
+      <c r="C6" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>31</v>
+      </c>
+      <c r="C7">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
+  <dimension ref="A1:C4"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.5703125" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1275,8 +1529,8 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>33</v>
+      <c r="B2" s="4" t="s">
+        <v>32</v>
       </c>
       <c r="C2">
         <v>43707</v>
@@ -1286,44 +1540,22 @@
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>38</v>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C3" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:3">
       <c r="A4" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="5" t="s">
+      <c r="C4" t="s">
         <v>35</v>
-      </c>
-      <c r="C6" t="s">
-        <v>36</v>
       </c>
     </row>
   </sheetData>
@@ -1332,13 +1564,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652FB01D-588D-4E1E-B4E4-BDE81F8D2A81}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1356,69 +1588,44 @@
       <c r="A2" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" t="s">
-        <v>37</v>
+      <c r="B2" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
       </c>
     </row>
     <row r="3" spans="1:3">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="5" t="s">
-        <v>35</v>
+      <c r="B3" s="4" t="s">
+        <v>33</v>
       </c>
       <c r="C3" t="s">
         <v>36</v>
       </c>
     </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
-  <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="5" t="s">
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>33</v>
+      </c>
+      <c r="C4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="C2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="C3">
-        <v>43707</v>
+      <c r="C5" t="s">
+        <v>35</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProductClassic\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation New\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F932A1-CB9F-40EF-910E-5C8DCE140DFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17329C90-DD99-40E7-8272-536EA444C35C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" firstSheet="5" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="2" activeTab="6" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="63">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -204,13 +204,37 @@
   </si>
   <si>
     <t>Files and Forms: Notes</t>
+  </si>
+  <si>
+    <t>Pre-application abstract description</t>
+  </si>
+  <si>
+    <t>Pre-application goals description</t>
+  </si>
+  <si>
+    <t>Pre-application beneficiary description</t>
+  </si>
+  <si>
+    <t>Pre - application justification for project cost</t>
+  </si>
+  <si>
+    <t>fieldPROGRAMINCOME__c</t>
+  </si>
+  <si>
+    <t>Providing Department of helath services</t>
+  </si>
+  <si>
+    <t>Focus on timeline to complete project</t>
+  </si>
+  <si>
+    <t>David bobs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -243,6 +267,12 @@
       <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -264,7 +294,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -282,6 +312,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -598,10 +632,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE61A50-F37E-45CB-A9C9-9EE192BF6C64}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -667,10 +701,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -748,10 +782,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -795,10 +829,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -842,10 +876,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.1796875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -955,10 +989,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="20.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1035,10 +1069,10 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1115,10 +1149,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="23.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.54296875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1151,11 +1185,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" customWidth="1"/>
+    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1177,7 +1211,7 @@
         <v>52</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1188,7 +1222,7 @@
         <v>51</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1199,7 +1233,7 @@
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1215,13 +1249,24 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B7" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
+      <c r="C7" t="s">
+        <v>58</v>
       </c>
     </row>
   </sheetData>
@@ -1233,10 +1278,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="10.85546875" customWidth="1"/>
-    <col min="2" max="2" width="11.5703125" customWidth="1"/>
+    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="2" max="2" width="11.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1302,10 +1347,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="21.85546875" customWidth="1"/>
-    <col min="3" max="3" width="52.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.81640625" customWidth="1"/>
+    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1371,9 +1416,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD30DDC9-54F2-4EA2-B2D6-C4D0607FC1E9}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="30.42578125" customWidth="1"/>
+    <col min="2" max="2" width="30.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1417,10 +1462,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="29.5703125" customWidth="1"/>
-    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="2" max="2" width="29.54296875" customWidth="1"/>
+    <col min="3" max="3" width="34.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1442,7 +1487,7 @@
         <v>24</v>
       </c>
       <c r="C2" t="s">
-        <v>25</v>
+        <v>60</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1453,7 +1498,7 @@
         <v>26</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1486,7 +1531,7 @@
         <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -1508,10 +1553,10 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="43.5703125" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" customWidth="1"/>
+    <col min="2" max="2" width="43.54296875" customWidth="1"/>
+    <col min="3" max="3" width="22.54296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1567,10 +1612,10 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{652FB01D-588D-4E1E-B4E4-BDE81F8D2A81}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="2" max="2" width="38.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.7265625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.1796875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27726"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Demo Data Creation 3.0\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5CA0F7-F9D8-4281-9FA3-82B3F81331BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224E3FF2-578C-4C3D-AE4F-BAF754DF32A3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="5" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="57">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -196,13 +196,37 @@
   </si>
   <si>
     <t>ApplicantResponse__c</t>
+  </si>
+  <si>
+    <t>Pre-application abstract description</t>
+  </si>
+  <si>
+    <t>Pre-application goals description</t>
+  </si>
+  <si>
+    <t>Pre-application beneficiary description</t>
+  </si>
+  <si>
+    <t>PROGRAMINCOME__c</t>
+  </si>
+  <si>
+    <t>Pre - application justification for project cost</t>
+  </si>
+  <si>
+    <t>Providing Department of helath services</t>
+  </si>
+  <si>
+    <t>Focus on timeline to complete project</t>
+  </si>
+  <si>
+    <t>David bobs</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -235,6 +259,12 @@
       <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="6"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -256,7 +286,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -274,6 +304,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1062,7 +1096,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="21.90625" customWidth="1"/>
@@ -1088,7 +1122,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>49</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1099,7 +1133,7 @@
         <v>16</v>
       </c>
       <c r="C3" t="s">
-        <v>21</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1110,7 +1144,7 @@
         <v>17</v>
       </c>
       <c r="C4" t="s">
-        <v>20</v>
+        <v>51</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -1126,13 +1160,24 @@
     </row>
     <row r="6" spans="1:3">
       <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="9">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7" t="s">
         <v>18</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" t="s">
-        <v>19</v>
+      <c r="C7" t="s">
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -1307,7 +1352,7 @@
         <v>39</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -1318,7 +1363,7 @@
         <v>40</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -1351,7 +1396,7 @@
         <v>43</v>
       </c>
       <c r="C6" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:3">

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A5CA0F7-F9D8-4281-9FA3-82B3F81331BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55FF986-5243-4F90-AFA9-E0C609479D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="1" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="50">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -196,6 +196,9 @@
   </si>
   <si>
     <t>ApplicantResponse__c</t>
+  </si>
+  <si>
+    <t>Files and Forms: Notes</t>
   </si>
 </sst>
 </file>
@@ -256,7 +259,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -274,6 +277,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -590,10 +596,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9AE61A50-F37E-45CB-A9C9-9EE192BF6C64}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -659,10 +665,10 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -706,10 +712,10 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
   <dimension ref="A1:C3"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -753,10 +759,10 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -866,10 +872,10 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="20.453125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="43.1796875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="43.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -946,10 +952,10 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
     <col min="2" max="2" width="27" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="14.6328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1026,10 +1032,10 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{70B87285-F8C8-4985-8D64-B234A73C3C3A}">
   <dimension ref="A1:C2"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="23.6328125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="37.08984375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="23.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="37.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1063,10 +1069,10 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C033547B-D4AA-4CF2-A8D1-414367FC6855}">
   <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.90625" customWidth="1"/>
-    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1144,10 +1150,10 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="1" max="1" width="10.90625" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="10.88671875" customWidth="1"/>
+    <col min="2" max="2" width="11.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
@@ -1213,10 +1219,10 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="21.90625" customWidth="1"/>
-    <col min="3" max="3" width="52.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="21.88671875" customWidth="1"/>
+    <col min="3" max="3" width="52.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1282,10 +1288,10 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="29.54296875" customWidth="1"/>
-    <col min="3" max="3" width="20.36328125" customWidth="1"/>
+    <col min="2" max="2" width="29.5546875" customWidth="1"/>
+    <col min="3" max="3" width="20.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1373,10 +1379,10 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="43.6328125" customWidth="1"/>
-    <col min="3" max="3" width="22.54296875" customWidth="1"/>
+    <col min="2" max="2" width="43.6640625" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1431,64 +1437,11 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0ADD10-8CE2-43FE-B59D-D33E800DC8BE}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="38.81640625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>47</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.5"/>
-  <cols>
-    <col min="2" max="2" width="43.08984375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.54296875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
@@ -1509,6 +1462,75 @@
       <c r="B2" s="4" t="s">
         <v>45</v>
       </c>
+      <c r="C2" s="8">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>45</v>
+      </c>
       <c r="C2">
         <v>43707</v>
       </c>

--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -1,32 +1,33 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E55FF986-5243-4F90-AFA9-E0C609479D16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F19528-5EB6-44F3-94FF-0EC74A65F5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="8" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="3" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
     <sheet name="Creation" sheetId="1" r:id="rId2"/>
     <sheet name="Edition" sheetId="4" r:id="rId3"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId4"/>
-    <sheet name="Edition1" sheetId="5" r:id="rId5"/>
-    <sheet name="Form_Edit" sheetId="6" r:id="rId6"/>
-    <sheet name="Negotiation_Edit" sheetId="7" r:id="rId7"/>
-    <sheet name="Nego_Edit_Notes" sheetId="16" r:id="rId8"/>
-    <sheet name="Nego_Edit1" sheetId="8" r:id="rId9"/>
-    <sheet name="FileFormForms" sheetId="9" r:id="rId10"/>
-    <sheet name="FileFormForms1" sheetId="10" r:id="rId11"/>
-    <sheet name="FileFormForms2" sheetId="11" r:id="rId12"/>
-    <sheet name="Edition_v" sheetId="12" r:id="rId13"/>
-    <sheet name="Form_v" sheetId="13" r:id="rId14"/>
+    <sheet name="Grantee_Edition" sheetId="17" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId5"/>
+    <sheet name="Edition1" sheetId="5" r:id="rId6"/>
+    <sheet name="Form_Edit" sheetId="6" r:id="rId7"/>
+    <sheet name="Negotiation_Edit" sheetId="7" r:id="rId8"/>
+    <sheet name="Nego_Edit_Notes" sheetId="16" r:id="rId9"/>
+    <sheet name="Nego_Edit1" sheetId="8" r:id="rId10"/>
+    <sheet name="FileFormForms" sheetId="9" r:id="rId11"/>
+    <sheet name="FileFormForms1" sheetId="10" r:id="rId12"/>
+    <sheet name="FileFormForms2" sheetId="11" r:id="rId13"/>
+    <sheet name="Edition_v" sheetId="12" r:id="rId14"/>
+    <sheet name="Form_v" sheetId="13" r:id="rId15"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -49,7 +50,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="55">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -199,6 +200,21 @@
   </si>
   <si>
     <t>Files and Forms: Notes</t>
+  </si>
+  <si>
+    <t>YRNMVN96JC17</t>
+  </si>
+  <si>
+    <t>DUNS__c</t>
+  </si>
+  <si>
+    <t>Victor EXE</t>
+  </si>
+  <si>
+    <t>Line Item Budget</t>
+  </si>
+  <si>
+    <t>BudgetBuildupNeeded__c</t>
   </si>
 </sst>
 </file>
@@ -663,6 +679,87 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C6" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -709,7 +806,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -756,7 +853,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -869,7 +966,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -949,7 +1046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1148,6 +1245,75 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A2AA710F-C461-47BD-BF99-2785E84D8984}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="20.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.88671875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" t="s">
+        <v>53</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1216,7 +1382,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1285,7 +1451,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1376,7 +1542,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1435,7 +1601,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0ADD10-8CE2-43FE-B59D-D33E800DC8BE}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1502,85 +1668,4 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="43.109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="45.5546875" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2">
-        <v>43707</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>
--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -8,26 +8,27 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{50F19528-5EB6-44F3-94FF-0EC74A65F5C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC2D771-F233-47BA-B236-CD44BB42809C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="3" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="4" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
   <sheets>
     <sheet name="Negotiation_Edit_Budget" sheetId="15" r:id="rId1"/>
     <sheet name="Creation" sheetId="1" r:id="rId2"/>
     <sheet name="Edition" sheetId="4" r:id="rId3"/>
     <sheet name="Grantee_Edition" sheetId="17" r:id="rId4"/>
-    <sheet name="Sheet1" sheetId="3" r:id="rId5"/>
-    <sheet name="Edition1" sheetId="5" r:id="rId6"/>
-    <sheet name="Form_Edit" sheetId="6" r:id="rId7"/>
-    <sheet name="Negotiation_Edit" sheetId="7" r:id="rId8"/>
-    <sheet name="Nego_Edit_Notes" sheetId="16" r:id="rId9"/>
-    <sheet name="Nego_Edit1" sheetId="8" r:id="rId10"/>
-    <sheet name="FileFormForms" sheetId="9" r:id="rId11"/>
-    <sheet name="FileFormForms1" sheetId="10" r:id="rId12"/>
-    <sheet name="FileFormForms2" sheetId="11" r:id="rId13"/>
-    <sheet name="Edition_v" sheetId="12" r:id="rId14"/>
-    <sheet name="Form_v" sheetId="13" r:id="rId15"/>
+    <sheet name="Grantee_Edition_DetailLineItems" sheetId="18" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="3" r:id="rId6"/>
+    <sheet name="Edition1" sheetId="5" r:id="rId7"/>
+    <sheet name="Form_Edit" sheetId="6" r:id="rId8"/>
+    <sheet name="Negotiation_Edit" sheetId="7" r:id="rId9"/>
+    <sheet name="Nego_Edit_Notes" sheetId="16" r:id="rId10"/>
+    <sheet name="Nego_Edit1" sheetId="8" r:id="rId11"/>
+    <sheet name="FileFormForms" sheetId="9" r:id="rId12"/>
+    <sheet name="FileFormForms1" sheetId="10" r:id="rId13"/>
+    <sheet name="FileFormForms2" sheetId="11" r:id="rId14"/>
+    <sheet name="Edition_v" sheetId="12" r:id="rId15"/>
+    <sheet name="Form_v" sheetId="13" r:id="rId16"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="235" uniqueCount="56">
   <si>
     <t>Sub Tab</t>
   </si>
@@ -215,13 +216,16 @@
   </si>
   <si>
     <t>BudgetBuildupNeeded__c</t>
+  </si>
+  <si>
+    <t>Detailed Line Item Budget</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -254,6 +258,12 @@
       <name val="JetBrains Mono"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="7"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -275,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -297,6 +307,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -679,6 +690,75 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0ADD10-8CE2-43FE-B59D-D33E800DC8BE}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="C2" s="8">
+        <v>43707</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>26</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39C679EE-FB70-45F3-9EAA-C420A1BC0CCC}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -759,7 +839,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{807D8089-D0B0-43AA-8E89-0290C512B75C}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -806,7 +886,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B98F735-DEB5-4E54-9C6E-D31529E5650A}">
   <dimension ref="A1:C3"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -853,7 +933,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C49BDFF5-26F4-4436-BD8F-B22E6FD646B3}">
   <dimension ref="A1:C9"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -966,7 +1046,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B90EF293-2340-46F3-9D02-1FC1787C0DF5}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1046,7 +1126,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F68EE05-8E2F-4CEF-958E-B563CAF4F33B}">
   <dimension ref="A1:C6"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1314,6 +1394,75 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33497124-79D7-4FC3-819E-F36EFE3FBD39}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultRowHeight="14.4"/>
+  <cols>
+    <col min="2" max="2" width="23.109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C2" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5" t="s">
+        <v>18</v>
+      </c>
+      <c r="B5" t="s">
+        <v>54</v>
+      </c>
+      <c r="C5" s="9" t="s">
+        <v>55</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8676E538-BD44-4E88-B93C-585B884C6D39}">
   <dimension ref="A1:C18"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1382,7 +1531,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA14F82A-41BD-4CF1-B3FF-A0476D7897D2}">
   <dimension ref="A1:C5"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1451,7 +1600,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CACF8178-9A74-4FB0-9CB5-F6DF3BEF9DB2}">
   <dimension ref="A1:C7"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1542,7 +1691,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{33A8B75B-19BE-4B0B-BC23-5F4209BE74EC}">
   <dimension ref="A1:C4"/>
   <sheetFormatPr defaultRowHeight="14.4"/>
@@ -1599,73 +1748,4 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8B0ADD10-8CE2-43FE-B59D-D33E800DC8BE}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
-  <cols>
-    <col min="2" max="2" width="38.77734375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.6640625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="C2" s="8">
-        <v>43707</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>4</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>46</v>
-      </c>
-      <c r="C4" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="C5" t="s">
-        <v>26</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/src/main/resources/PreApplication_Field_Values.xlsx
+++ b/src/main/resources/PreApplication_Field_Values.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\New LWC\govgrants-product-automation\src\main\resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9FC2D771-F233-47BA-B236-CD44BB42809C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38890B7E-7740-4F35-B1FA-1AE0F0C3E351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" firstSheet="2" activeTab="4" xr2:uid="{24C7FA98-EA31-489A-B4B9-70B882520CBB}"/>
   </bookViews>
